--- a/Found_Malicious_Models_HF.xlsx
+++ b/Found_Malicious_Models_HF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ML_Project_2026\ACSAC\1.final_artifacts\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ML_Project_2026\ACSAC\2.final_artifacts\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761DC3D6-F5A7-4EC4-9330-63A670E26272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3A3721-5B0A-4BF7-986B-62EAD775CC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{04670FFF-DBFA-4277-80BE-E624778C8932}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{04670FFF-DBFA-4277-80BE-E624778C8932}"/>
   </bookViews>
   <sheets>
     <sheet name="41_Malicious Models" sheetId="1" r:id="rId1"/>
@@ -4529,6 +4529,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4538,14 +4547,17 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4555,18 +4567,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4940,77 +4940,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="37" customFormat="1" ht="37.799999999999997" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="52" t="s">
         <v>881</v>
       </c>
-      <c r="F1" s="47"/>
-      <c r="G1" s="48" t="s">
+      <c r="F1" s="52"/>
+      <c r="G1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="47" t="s">
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46" t="s">
+      <c r="N1" s="51"/>
+      <c r="O1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46" t="s">
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51" t="s">
         <v>504</v>
       </c>
-      <c r="S1" s="46" t="s">
+      <c r="S1" s="51" t="s">
         <v>541</v>
       </c>
-      <c r="T1" s="46" t="s">
+      <c r="T1" s="51" t="s">
         <v>543</v>
       </c>
-      <c r="U1" s="46" t="s">
+      <c r="U1" s="51" t="s">
         <v>542</v>
       </c>
-      <c r="V1" s="46" t="s">
+      <c r="V1" s="51" t="s">
         <v>528</v>
       </c>
-      <c r="W1" s="46" t="s">
+      <c r="W1" s="51" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:24" s="37" customFormat="1" ht="43.2" customHeight="1">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
       <c r="E2" s="36" t="s">
         <v>882</v>
       </c>
       <c r="F2" s="36" t="s">
         <v>883</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="46"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="51"/>
       <c r="I2" s="35" t="s">
         <v>40</v>
       </c>
@@ -5020,7 +5020,7 @@
       <c r="K2" s="36" t="s">
         <v>908</v>
       </c>
-      <c r="L2" s="47"/>
+      <c r="L2" s="52"/>
       <c r="M2" s="38" t="s">
         <v>56</v>
       </c>
@@ -5036,12 +5036,12 @@
       <c r="Q2" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
     </row>
     <row r="3" spans="1:24" s="13" customFormat="1" ht="69" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -5201,10 +5201,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="22">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F5" s="22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>862</v>
@@ -5492,7 +5492,7 @@
         <v>23</v>
       </c>
       <c r="F9" s="20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>865</v>
@@ -6712,8 +6712,12 @@
       <c r="D26" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="22">
+        <v>0</v>
+      </c>
+      <c r="F26" s="22">
+        <v>0</v>
+      </c>
       <c r="G26" s="26" t="s">
         <v>868</v>
       </c>
@@ -7560,10 +7564,10 @@
         <v>400</v>
       </c>
       <c r="E38" s="20">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="F38" s="20">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G38" s="19" t="s">
         <v>401</v>
@@ -7631,10 +7635,10 @@
         <v>404</v>
       </c>
       <c r="E39" s="20">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F39" s="20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G39" s="25" t="s">
         <v>871</v>
@@ -7915,10 +7919,10 @@
         <v>533</v>
       </c>
       <c r="E43" s="22">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F43" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>878</v>
@@ -7973,11 +7977,11 @@
       </c>
     </row>
     <row r="45" spans="1:23" ht="57.6" customHeight="1">
-      <c r="A45" s="43" t="s">
+      <c r="A45" s="46" t="s">
         <v>884</v>
       </c>
-      <c r="B45" s="44"/>
-      <c r="C45" s="45"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="48"/>
       <c r="G45" s="12"/>
       <c r="M45" s="27"/>
       <c r="N45" s="28"/>
@@ -8005,6 +8009,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="W1:W2"/>
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="T1:T2"/>
@@ -8017,12 +8027,6 @@
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="E1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{AB12B4A2-43F7-4CA7-827D-F11FE676A967}"/>
@@ -8089,32 +8093,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.4" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="53" t="s">
         <v>881</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="54"/>
     </row>
     <row r="2" spans="1:13" ht="18">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
       <c r="F2" s="42" t="s">
         <v>882</v>
       </c>
@@ -10134,81 +10138,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="31" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="44" t="s">
         <v>909</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="53" t="s">
+      <c r="F1" s="45"/>
+      <c r="G1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="52" t="s">
+      <c r="I1" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52" t="s">
+      <c r="J1" s="50"/>
+      <c r="K1" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="48" t="s">
+      <c r="L1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48" t="s">
+      <c r="M1" s="49"/>
+      <c r="N1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48" t="s">
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49" t="s">
         <v>504</v>
       </c>
-      <c r="R1" s="48" t="s">
+      <c r="R1" s="49" t="s">
         <v>541</v>
       </c>
-      <c r="S1" s="48" t="s">
+      <c r="S1" s="49" t="s">
         <v>543</v>
       </c>
-      <c r="T1" s="48" t="s">
+      <c r="T1" s="49" t="s">
         <v>542</v>
       </c>
-      <c r="U1" s="48" t="s">
+      <c r="U1" s="49" t="s">
         <v>528</v>
       </c>
-      <c r="V1" s="48"/>
+      <c r="V1" s="49"/>
     </row>
     <row r="2" spans="1:22" s="31" customFormat="1" ht="18">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
       <c r="E2" s="34" t="s">
         <v>882</v>
       </c>
       <c r="F2" s="34" t="s">
         <v>883</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="50"/>
       <c r="I2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="J2" s="32" t="s">
         <v>549</v>
       </c>
-      <c r="K2" s="52"/>
+      <c r="K2" s="50"/>
       <c r="L2" s="32" t="s">
         <v>56</v>
       </c>
@@ -10224,12 +10228,12 @@
       <c r="P2" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
     </row>
     <row r="3" spans="1:22" s="19" customFormat="1" ht="43.2">
       <c r="A3" s="19" t="s">
@@ -17075,11 +17079,11 @@
       <c r="U109" s="20"/>
     </row>
     <row r="110" spans="1:22" ht="57.6" customHeight="1">
-      <c r="A110" s="43" t="s">
+      <c r="A110" s="46" t="s">
         <v>1036</v>
       </c>
-      <c r="B110" s="44"/>
-      <c r="C110" s="45"/>
+      <c r="B110" s="47"/>
+      <c r="C110" s="48"/>
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" s="12"/>
@@ -17130,6 +17134,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="K1:K2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A110:C110"/>
@@ -17139,15 +17152,6 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="K1:K2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" xr:uid="{E3C7E6AE-7D08-45CE-A193-AA3D6DF2D5B3}"/>
